--- a/mode_docx_gen/pmi_ka2/ka_modes/КА_11.xlsx
+++ b/mode_docx_gen/pmi_ka2/ka_modes/КА_11.xlsx
@@ -1122,8 +1122,8 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1206,8 +1206,8 @@
       <c r="AI2" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" s="2" t="n">
-        <v>1</v>
+      <c r="AJ2" t="n">
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -1517,144 +1517,144 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1672,9 +1672,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
